--- a/full/sliding_window_results_window_4.xlsx
+++ b/full/sliding_window_results_window_4.xlsx
@@ -463,13 +463,13 @@
         <v>29.37</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>28.27788229977268</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.37</v>
+        <v>-1.092117700227323</v>
       </c>
       <c r="E2" t="n">
-        <v>862.5969</v>
+        <v>1.192721071149818</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.54</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>29.19175924173338</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.54</v>
+        <v>-0.3482407582666198</v>
       </c>
       <c r="E3" t="n">
-        <v>872.6116</v>
+        <v>0.1212716257181103</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.55</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>30.09155300362499</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.55</v>
+        <v>0.541553003624994</v>
       </c>
       <c r="E4" t="n">
-        <v>873.2025</v>
+        <v>0.2932796557352528</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.75</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>29.78267262292169</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.75</v>
+        <v>0.03267262292168738</v>
       </c>
       <c r="E5" t="n">
-        <v>885.0625</v>
+        <v>0.001067500288582771</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.84</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>29.75900732942098</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.84</v>
+        <v>-0.08099267057901827</v>
       </c>
       <c r="E6" t="n">
-        <v>890.4256</v>
+        <v>0.006559812687521371</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.81</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>29.84561044431663</v>
       </c>
       <c r="D7" t="n">
-        <v>-29.81</v>
+        <v>0.03561044431662808</v>
       </c>
       <c r="E7" t="n">
-        <v>888.6360999999999</v>
+        <v>0.001268103744427669</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.92</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>29.62121671700346</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.92</v>
+        <v>-0.2987832829965384</v>
       </c>
       <c r="E8" t="n">
-        <v>895.2064000000001</v>
+        <v>0.08927145019818958</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.98</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>29.83432592272917</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.98</v>
+        <v>-0.1456740772708294</v>
       </c>
       <c r="E9" t="n">
-        <v>898.8004000000001</v>
+        <v>0.02122093678870757</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.04</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>29.88982670961775</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.04</v>
+        <v>-0.1501732903822486</v>
       </c>
       <c r="E10" t="n">
-        <v>902.4015999999999</v>
+        <v>0.02255201714423116</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.21</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>29.78883031723733</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.21</v>
+        <v>-0.4211696827626668</v>
       </c>
       <c r="E11" t="n">
-        <v>912.6441000000001</v>
+        <v>0.1773839016784053</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.22</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.16589280729863</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.22</v>
+        <v>-0.05410719270137321</v>
       </c>
       <c r="E12" t="n">
-        <v>913.2483999999999</v>
+        <v>0.002927588302023534</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.38</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>29.82036427603519</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.38</v>
+        <v>-0.5596357239648135</v>
       </c>
       <c r="E13" t="n">
-        <v>922.9444</v>
+        <v>0.313192143537621</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.44</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>30.05698656662453</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.44</v>
+        <v>-0.3830134333754707</v>
       </c>
       <c r="E14" t="n">
-        <v>926.5936</v>
+        <v>0.1466992901460661</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.48</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>30.19023929771748</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.48</v>
+        <v>-0.2897607022825248</v>
       </c>
       <c r="E15" t="n">
-        <v>929.0304</v>
+        <v>0.08396126458726198</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.69</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>29.96611093429973</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.69</v>
+        <v>-0.7238890657002663</v>
       </c>
       <c r="E16" t="n">
-        <v>941.8761000000001</v>
+        <v>0.5240153794404045</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.75</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>29.95353145807043</v>
       </c>
       <c r="D17" t="n">
-        <v>-30.75</v>
+        <v>-0.7964685419295705</v>
       </c>
       <c r="E17" t="n">
-        <v>945.5625</v>
+        <v>0.634362138283416</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.94</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>30.54948913695124</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.94</v>
+        <v>-0.3905108630487568</v>
       </c>
       <c r="E18" t="n">
-        <v>957.2836000000001</v>
+        <v>0.1524987341590849</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.95</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>30.77586982982714</v>
       </c>
       <c r="D19" t="n">
-        <v>-30.95</v>
+        <v>-0.1741301701728553</v>
       </c>
       <c r="E19" t="n">
-        <v>957.9024999999999</v>
+        <v>0.03032131616442753</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.02</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>30.70160810776703</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.02</v>
+        <v>-0.3183918922329703</v>
       </c>
       <c r="E20" t="n">
-        <v>962.2404</v>
+        <v>0.1013733970396914</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.12</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>30.78623034825427</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.12</v>
+        <v>-0.3337696517457296</v>
       </c>
       <c r="E21" t="n">
-        <v>968.4544000000001</v>
+        <v>0.1114021804264656</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.28</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.27141867503842</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.28</v>
+        <v>-0.008581324961582482</v>
       </c>
       <c r="E22" t="n">
-        <v>978.4384000000001</v>
+        <v>7.363913809627858e-05</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.38</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>31.3953411648987</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.38</v>
+        <v>0.01534116489870385</v>
       </c>
       <c r="E23" t="n">
-        <v>984.7044</v>
+        <v>0.0002353513404492232</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.58</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>31.58726286396578</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.58</v>
+        <v>0.00726286396577791</v>
       </c>
       <c r="E24" t="n">
-        <v>997.2963999999999</v>
+        <v>5.274919298539523e-05</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.65</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>31.5674891895968</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.65</v>
+        <v>-0.08251081040319974</v>
       </c>
       <c r="E25" t="n">
-        <v>1001.7225</v>
+        <v>0.006808033833392775</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.88</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>31.90485810887399</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.88</v>
+        <v>0.02485810887398898</v>
       </c>
       <c r="E26" t="n">
-        <v>1016.3344</v>
+        <v>0.0006179255767910898</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.28</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>32.29400698910788</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.28</v>
+        <v>0.01400698910787668</v>
       </c>
       <c r="E27" t="n">
-        <v>1041.9984</v>
+        <v>0.0001961957438681759</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.45</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>32.24138097474844</v>
       </c>
       <c r="D28" t="n">
-        <v>-32.45</v>
+        <v>-0.2086190252515649</v>
       </c>
       <c r="E28" t="n">
-        <v>1053.0025</v>
+        <v>0.04352189769691309</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.85</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>33.52817252141637</v>
       </c>
       <c r="D29" t="n">
-        <v>-32.85</v>
+        <v>0.6781725214163714</v>
       </c>
       <c r="E29" t="n">
-        <v>1079.1225</v>
+        <v>0.4599179688042387</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.9</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>33.28296385789197</v>
       </c>
       <c r="D30" t="n">
-        <v>-32.9</v>
+        <v>0.3829638578919727</v>
       </c>
       <c r="E30" t="n">
-        <v>1082.41</v>
+        <v>0.1466613164515031</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.1</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>33.3784015109037</v>
       </c>
       <c r="D31" t="n">
-        <v>-33.1</v>
+        <v>0.2784015109036986</v>
       </c>
       <c r="E31" t="n">
-        <v>1095.61</v>
+        <v>0.0775074012734622</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.4</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>33.25763537194656</v>
       </c>
       <c r="D32" t="n">
-        <v>-33.4</v>
+        <v>-0.1423646280534356</v>
       </c>
       <c r="E32" t="n">
-        <v>1115.56</v>
+        <v>0.02026768732079307</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.7</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>33.94127858902861</v>
       </c>
       <c r="D33" t="n">
-        <v>-33.7</v>
+        <v>0.2412785890286031</v>
       </c>
       <c r="E33" t="n">
-        <v>1135.69</v>
+        <v>0.05821535752363356</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>34.80115297861217</v>
       </c>
       <c r="D34" t="n">
-        <v>-34.1</v>
+        <v>0.7011529786121642</v>
       </c>
       <c r="E34" t="n">
-        <v>1162.81</v>
+        <v>0.49161549941671</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.4</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>34.71223657580823</v>
       </c>
       <c r="D35" t="n">
-        <v>-34.4</v>
+        <v>0.3122365758082282</v>
       </c>
       <c r="E35" t="n">
-        <v>1183.36</v>
+        <v>0.09749167927244741</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.9</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>35.20854410149703</v>
       </c>
       <c r="D36" t="n">
-        <v>-34.9</v>
+        <v>0.3085441014970343</v>
       </c>
       <c r="E36" t="n">
-        <v>1218.01</v>
+        <v>0.09519946256861218</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.3</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>35.00070622077768</v>
       </c>
       <c r="D37" t="n">
-        <v>-35.3</v>
+        <v>-0.2992937792223174</v>
       </c>
       <c r="E37" t="n">
-        <v>1246.09</v>
+        <v>0.08957676628117725</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.7</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>35.39205346563158</v>
       </c>
       <c r="D38" t="n">
-        <v>-35.7</v>
+        <v>-0.3079465343684191</v>
       </c>
       <c r="E38" t="n">
-        <v>1274.49</v>
+        <v>0.09483106802951995</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>35.98064298204398</v>
       </c>
       <c r="D39" t="n">
-        <v>-36.3</v>
+        <v>-0.3193570179560155</v>
       </c>
       <c r="E39" t="n">
-        <v>1317.69</v>
+        <v>0.1019889049177588</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.8</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>36.42452701316659</v>
       </c>
       <c r="D40" t="n">
-        <v>-36.8</v>
+        <v>-0.3754729868334081</v>
       </c>
       <c r="E40" t="n">
-        <v>1354.24</v>
+        <v>0.1409799638416007</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.3</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>37.51103321642204</v>
       </c>
       <c r="D41" t="n">
-        <v>-37.3</v>
+        <v>0.2110332164220452</v>
       </c>
       <c r="E41" t="n">
-        <v>1391.29</v>
+        <v>0.04453501843343377</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.9</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>38.35515710999172</v>
       </c>
       <c r="D42" t="n">
-        <v>-37.9</v>
+        <v>0.455157109991724</v>
       </c>
       <c r="E42" t="n">
-        <v>1436.41</v>
+        <v>0.2071679947760183</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.5</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>38.90910449529751</v>
       </c>
       <c r="D43" t="n">
-        <v>-38.5</v>
+        <v>0.4091044952975125</v>
       </c>
       <c r="E43" t="n">
-        <v>1482.25</v>
+        <v>0.1673664880726324</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.9</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>39.76024284485575</v>
       </c>
       <c r="D44" t="n">
-        <v>-38.9</v>
+        <v>0.8602428448557546</v>
       </c>
       <c r="E44" t="n">
-        <v>1513.21</v>
+        <v>0.7400177521255219</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.4</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>40.40243169098477</v>
       </c>
       <c r="D45" t="n">
-        <v>-39.4</v>
+        <v>1.002431690984771</v>
       </c>
       <c r="E45" t="n">
-        <v>1552.36</v>
+        <v>1.004869295090588</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.9</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>40.64866100100531</v>
       </c>
       <c r="D46" t="n">
-        <v>-39.9</v>
+        <v>0.7486610010053099</v>
       </c>
       <c r="E46" t="n">
-        <v>1592.01</v>
+        <v>0.5604932944262726</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>39.58036945558321</v>
       </c>
       <c r="D47" t="n">
-        <v>-40.1</v>
+        <v>-0.5196305444167919</v>
       </c>
       <c r="E47" t="n">
-        <v>1608.01</v>
+        <v>0.2700159026908915</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.6</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>40.98050448704024</v>
       </c>
       <c r="D48" t="n">
-        <v>-40.6</v>
+        <v>0.3805044870402341</v>
       </c>
       <c r="E48" t="n">
-        <v>1648.36</v>
+        <v>0.1447836646577517</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.9</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>41.08319000266954</v>
       </c>
       <c r="D49" t="n">
-        <v>-40.9</v>
+        <v>0.1831900026695408</v>
       </c>
       <c r="E49" t="n">
-        <v>1672.81</v>
+        <v>0.03355857707806636</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.2</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>40.76523899808499</v>
       </c>
       <c r="D50" t="n">
-        <v>-41.2</v>
+        <v>-0.4347610019150139</v>
       </c>
       <c r="E50" t="n">
-        <v>1697.44</v>
+        <v>0.1890171287861467</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.5</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>40.21752257365866</v>
       </c>
       <c r="D51" t="n">
-        <v>-41.5</v>
+        <v>-1.282477426341345</v>
       </c>
       <c r="E51" t="n">
-        <v>1722.25</v>
+        <v>1.644748349075119</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1677.15</v>
+        <v>-2.717463598228047</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>56961.7035</v>
+        <v>10.9596818406561</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1139.23407</v>
+        <v>0.2191936368131221</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_4.xlsx
+++ b/full/sliding_window_results_window_4.xlsx
@@ -463,13 +463,13 @@
         <v>29.37</v>
       </c>
       <c r="C2" t="n">
-        <v>28.27788229977268</v>
+        <v>28.92059861741942</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.092117700227323</v>
+        <v>-0.4494013825805858</v>
       </c>
       <c r="E2" t="n">
-        <v>1.192721071149818</v>
+        <v>0.201961602665342</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.54</v>
       </c>
       <c r="C3" t="n">
-        <v>29.19175924173338</v>
+        <v>29.4208909723817</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3482407582666198</v>
+        <v>-0.119109027618304</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1212716257181103</v>
+        <v>0.0141869604601779</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.55</v>
       </c>
       <c r="C4" t="n">
-        <v>30.09155300362499</v>
+        <v>29.57810467996173</v>
       </c>
       <c r="D4" t="n">
-        <v>0.541553003624994</v>
+        <v>0.02810467996172861</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2932796557352528</v>
+        <v>0.0007898730357511895</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.75</v>
       </c>
       <c r="C5" t="n">
-        <v>29.78267262292169</v>
+        <v>29.6035835095347</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03267262292168738</v>
+        <v>-0.1464164904653025</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001067500288582771</v>
+        <v>0.02143778868017601</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.84</v>
       </c>
       <c r="C6" t="n">
-        <v>29.75900732942098</v>
+        <v>29.76469066998424</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08099267057901827</v>
+        <v>-0.0753093300157559</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006559812687521371</v>
+        <v>0.005671495187422033</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.81</v>
       </c>
       <c r="C7" t="n">
-        <v>29.84561044431663</v>
+        <v>29.89437926190208</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03561044431662808</v>
+        <v>0.08437926190207889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001268103744427669</v>
+        <v>0.007119859839139622</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.92</v>
       </c>
       <c r="C8" t="n">
-        <v>29.62121671700346</v>
+        <v>29.9061988069463</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2987832829965384</v>
+        <v>-0.01380119305370542</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08927145019818958</v>
+        <v>0.0001904729297056467</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.98</v>
       </c>
       <c r="C9" t="n">
-        <v>29.83432592272917</v>
+        <v>29.98453038637416</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1456740772708294</v>
+        <v>0.004530386374163697</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02122093678870757</v>
+        <v>2.052440069920809e-05</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.04</v>
       </c>
       <c r="C10" t="n">
-        <v>29.88982670961775</v>
+        <v>29.99878220088704</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1501732903822486</v>
+        <v>-0.04121779911295675</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02255201714423116</v>
+        <v>0.001698906963716059</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.21</v>
       </c>
       <c r="C11" t="n">
-        <v>29.78883031723733</v>
+        <v>29.83638729647601</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4211696827626668</v>
+        <v>-0.3736127035239925</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1773839016784053</v>
+        <v>0.1395864522345067</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.22</v>
       </c>
       <c r="C12" t="n">
-        <v>30.16589280729863</v>
+        <v>29.94021448791692</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.05410719270137321</v>
+        <v>-0.2797855120830803</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002927588302023534</v>
+        <v>0.0782799327715915</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.38</v>
       </c>
       <c r="C13" t="n">
-        <v>29.82036427603519</v>
+        <v>29.93798284085615</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5596357239648135</v>
+        <v>-0.4420171591438447</v>
       </c>
       <c r="E13" t="n">
-        <v>0.313192143537621</v>
+        <v>0.1953791689775949</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.44</v>
       </c>
       <c r="C14" t="n">
-        <v>30.05698656662453</v>
+        <v>30.06464318532541</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3830134333754707</v>
+        <v>-0.3753568146745963</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1466992901460661</v>
+        <v>0.1408927383226592</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.48</v>
       </c>
       <c r="C15" t="n">
-        <v>30.19023929771748</v>
+        <v>30.34482450938618</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2897607022825248</v>
+        <v>-0.1351754906138218</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08396126458726198</v>
+        <v>0.01827241326268744</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.69</v>
       </c>
       <c r="C16" t="n">
-        <v>29.96611093429973</v>
+        <v>30.5519912237145</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7238890657002663</v>
+        <v>-0.1380087762855027</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5240153794404045</v>
+        <v>0.01904642233182192</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.75</v>
       </c>
       <c r="C17" t="n">
-        <v>29.95353145807043</v>
+        <v>30.2834920035475</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7964685419295705</v>
+        <v>-0.4665079964524956</v>
       </c>
       <c r="E17" t="n">
-        <v>0.634362138283416</v>
+        <v>0.2176297107541217</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.94</v>
       </c>
       <c r="C18" t="n">
-        <v>30.54948913695124</v>
+        <v>30.77420883418771</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3905108630487568</v>
+        <v>-0.1657911658122906</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1524987341590849</v>
+        <v>0.02748671066139843</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.95</v>
       </c>
       <c r="C19" t="n">
-        <v>30.77586982982714</v>
+        <v>30.82560239876328</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1741301701728553</v>
+        <v>-0.1243976012367156</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03032131616442753</v>
+        <v>0.01547476319344891</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.02</v>
       </c>
       <c r="C20" t="n">
-        <v>30.70160810776703</v>
+        <v>31.02090230664197</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3183918922329703</v>
+        <v>0.000902306641972217</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1013733970396914</v>
+        <v>8.141572761471785e-07</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.12</v>
       </c>
       <c r="C21" t="n">
-        <v>30.78623034825427</v>
+        <v>31.19362784737535</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3337696517457296</v>
+        <v>0.07362784737535222</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1114021804264656</v>
+        <v>0.005421059909128161</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.28</v>
       </c>
       <c r="C22" t="n">
-        <v>31.27141867503842</v>
+        <v>31.38694715401145</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.008581324961582482</v>
+        <v>0.1069471540114506</v>
       </c>
       <c r="E22" t="n">
-        <v>7.363913809627858e-05</v>
+        <v>0.01143769375114894</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.38</v>
       </c>
       <c r="C23" t="n">
-        <v>31.3953411648987</v>
+        <v>31.56835892217772</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01534116489870385</v>
+        <v>0.18835892217772</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002353513404492232</v>
+        <v>0.03547908356395237</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.58</v>
       </c>
       <c r="C24" t="n">
-        <v>31.58726286396578</v>
+        <v>31.71036609562289</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00726286396577791</v>
+        <v>0.1303660956228967</v>
       </c>
       <c r="E24" t="n">
-        <v>5.274919298539523e-05</v>
+        <v>0.01699531888795824</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.65</v>
       </c>
       <c r="C25" t="n">
-        <v>31.5674891895968</v>
+        <v>31.55148405202135</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08251081040319974</v>
+        <v>-0.09851594797864394</v>
       </c>
       <c r="E25" t="n">
-        <v>0.006808033833392775</v>
+        <v>0.009705392006130879</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.88</v>
       </c>
       <c r="C26" t="n">
-        <v>31.90485810887399</v>
+        <v>31.74614822448455</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02485810887398898</v>
+        <v>-0.1338517755154491</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0006179255767910898</v>
+        <v>0.01791629780863819</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.28</v>
       </c>
       <c r="C27" t="n">
-        <v>32.29400698910788</v>
+        <v>31.97021544346967</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01400698910787668</v>
+        <v>-0.3097845565303317</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0001961957438681759</v>
+        <v>0.09596647146469425</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.45</v>
       </c>
       <c r="C28" t="n">
-        <v>32.24138097474844</v>
+        <v>32.00862592648797</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2086190252515649</v>
+        <v>-0.44137407351203</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04352189769691309</v>
+        <v>0.1948110727686028</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.85</v>
       </c>
       <c r="C29" t="n">
-        <v>33.52817252141637</v>
+        <v>33.11944227097141</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6781725214163714</v>
+        <v>0.2694422709714104</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4599179688042387</v>
+        <v>0.07259913738623093</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.9</v>
       </c>
       <c r="C30" t="n">
-        <v>33.28296385789197</v>
+        <v>32.68709124731073</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3829638578919727</v>
+        <v>-0.2129087526892732</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1466613164515031</v>
+        <v>0.04533013697170211</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.1</v>
       </c>
       <c r="C31" t="n">
-        <v>33.3784015109037</v>
+        <v>33.12918757548471</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2784015109036986</v>
+        <v>0.02918757548470552</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0775074012734622</v>
+        <v>0.0008519145626753826</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.4</v>
       </c>
       <c r="C32" t="n">
-        <v>33.25763537194656</v>
+        <v>33.19300614524708</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1423646280534356</v>
+        <v>-0.2069938547529162</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02026768732079307</v>
+        <v>0.04284645590547137</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.7</v>
       </c>
       <c r="C33" t="n">
-        <v>33.94127858902861</v>
+        <v>33.68738758336665</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2412785890286031</v>
+        <v>-0.01261241663335255</v>
       </c>
       <c r="E33" t="n">
-        <v>0.05821535752363356</v>
+        <v>0.0001590730533332681</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.1</v>
       </c>
       <c r="C34" t="n">
-        <v>34.80115297861217</v>
+        <v>34.33461901781687</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7011529786121642</v>
+        <v>0.2346190178168683</v>
       </c>
       <c r="E34" t="n">
-        <v>0.49161549941671</v>
+        <v>0.05504608352135199</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.4</v>
       </c>
       <c r="C35" t="n">
-        <v>34.71223657580823</v>
+        <v>34.35663595064122</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3122365758082282</v>
+        <v>-0.0433640493587788</v>
       </c>
       <c r="E35" t="n">
-        <v>0.09749167927244741</v>
+        <v>0.001880440776790604</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.9</v>
       </c>
       <c r="C36" t="n">
-        <v>35.20854410149703</v>
+        <v>35.02057780095911</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3085441014970343</v>
+        <v>0.1205778009591114</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09519946256861218</v>
+        <v>0.01453900608413509</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.3</v>
       </c>
       <c r="C37" t="n">
-        <v>35.00070622077768</v>
+        <v>34.69069613881452</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2992937792223174</v>
+        <v>-0.6093038611854737</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08957676628117725</v>
+        <v>0.3712511952555271</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.7</v>
       </c>
       <c r="C38" t="n">
-        <v>35.39205346563158</v>
+        <v>35.18301491427265</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3079465343684191</v>
+        <v>-0.5169850857273488</v>
       </c>
       <c r="E38" t="n">
-        <v>0.09483106802951995</v>
+        <v>0.2672735788645142</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.3</v>
       </c>
       <c r="C39" t="n">
-        <v>35.98064298204398</v>
+        <v>36.11413052812126</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3193570179560155</v>
+        <v>-0.185869471878739</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1019889049177588</v>
+        <v>0.03454746057648136</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.8</v>
       </c>
       <c r="C40" t="n">
-        <v>36.42452701316659</v>
+        <v>36.47588263653283</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3754729868334081</v>
+        <v>-0.3241173634671668</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1409799638416007</v>
+        <v>0.1050520653009075</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.3</v>
       </c>
       <c r="C41" t="n">
-        <v>37.51103321642204</v>
+        <v>37.26527358156678</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2110332164220452</v>
+        <v>-0.03472641843321611</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04453501843343377</v>
+        <v>0.001205924137198812</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.9</v>
       </c>
       <c r="C42" t="n">
-        <v>38.35515710999172</v>
+        <v>37.83035536928313</v>
       </c>
       <c r="D42" t="n">
-        <v>0.455157109991724</v>
+        <v>-0.06964463071686566</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2071679947760183</v>
+        <v>0.004850374587688588</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.5</v>
       </c>
       <c r="C43" t="n">
-        <v>38.90910449529751</v>
+        <v>38.20782921034095</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4091044952975125</v>
+        <v>-0.2921707896590533</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1673664880726324</v>
+        <v>0.08536377032999476</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.9</v>
       </c>
       <c r="C44" t="n">
-        <v>39.76024284485575</v>
+        <v>38.79874690646273</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8602428448557546</v>
+        <v>-0.1012530935372666</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7400177521255219</v>
+        <v>0.01025218895086647</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.4</v>
       </c>
       <c r="C45" t="n">
-        <v>40.40243169098477</v>
+        <v>39.27791486264044</v>
       </c>
       <c r="D45" t="n">
-        <v>1.002431690984771</v>
+        <v>-0.1220851373595551</v>
       </c>
       <c r="E45" t="n">
-        <v>1.004869295090588</v>
+        <v>0.01490478076410143</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.9</v>
       </c>
       <c r="C46" t="n">
-        <v>40.64866100100531</v>
+        <v>39.71471506819267</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7486610010053099</v>
+        <v>-0.1852849318073311</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5604932944262726</v>
+        <v>0.03433050595484733</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.1</v>
       </c>
       <c r="C47" t="n">
-        <v>39.58036945558321</v>
+        <v>40.07856438027741</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5196305444167919</v>
+        <v>-0.02143561972258823</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2700159026908915</v>
+        <v>0.0004594857928914134</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.6</v>
       </c>
       <c r="C48" t="n">
-        <v>40.98050448704024</v>
+        <v>40.43771069877619</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3805044870402341</v>
+        <v>-0.162289301223808</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1447836646577517</v>
+        <v>0.0263378172917119</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.9</v>
       </c>
       <c r="C49" t="n">
-        <v>41.08319000266954</v>
+        <v>41.08319549285482</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1831900026695408</v>
+        <v>0.1831954928548214</v>
       </c>
       <c r="E49" t="n">
-        <v>0.03355857707806636</v>
+        <v>0.03356058860232092</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.2</v>
       </c>
       <c r="C50" t="n">
-        <v>40.76523899808499</v>
+        <v>41.11070651837815</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4347610019150139</v>
+        <v>-0.08929348162185136</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1890171287861467</v>
+        <v>0.007973325860151906</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.5</v>
       </c>
       <c r="C51" t="n">
-        <v>40.21752257365866</v>
+        <v>40.73014514982777</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.282477426341345</v>
+        <v>-0.76985485017223</v>
       </c>
       <c r="E51" t="n">
-        <v>1.644748349075119</v>
+        <v>0.5926764903337067</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-2.717463598228047</v>
+        <v>-6.83538909400194</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>10.9596818406561</v>
+        <v>3.316150801854092</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.2191936368131221</v>
+        <v>0.06632301603708184</v>
       </c>
     </row>
   </sheetData>
